--- a/research/jinan_tuoguan_2026/济南托管调研_v1.xlsx
+++ b/research/jinan_tuoguan_2026/济南托管调研_v1.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'任务4_企查查'!$A$1:$H$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'任务5_政府政策'!$A$1:$H$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'任务6_小红书'!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'任务7_抖音同城'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'任务7_抖音同城'!$A$1:$E$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'任务8_场地租金'!$A$1:$F$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'任务9_人工成本'!$A$1:$E$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'任务10_学一家'!$A$1:$E$23</definedName>
@@ -11588,14 +11588,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="100" customWidth="1" min="4" max="4"/>
+    <col width="72" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -11625,8 +11625,3572 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>94年小王｜盘锦初中晚自习托管</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>卖点=实验中学新初一家长注意；爱顿校区安可托管中心环境展示；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>万小妹</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>卖点=济南最美学校，绿城育华杨柳春风学校食堂；一蔬一饭藏教养；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>东街小学欣悦托辅</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>卖点=托管班大门已敞开，等待热爱学习的小小探索者 #开学季 #招生季；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>乐思托辅</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>卖点=实验中学校区托管，只有12个床位，招满即可；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>乐恩托管</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>卖点=每一刻都值得被记录 #泉海学校 #乐恩托管 #晚辅日常；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>云朵中心</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>卖点=开学前一天校区安全、卫生标准讲解；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>六六托管中心闫老师🙋（高端，专业）</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>卖点=#托管 #济南；一心只做托管，用心用爱撑起托管的孩子！；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>努力的龙</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>卖点=谁家托管点100杯果汁啊 #托管班 #托管上班日常；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>十七小学繁星托管</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>卖点=开学两个星期了；做托管的是良心，尽心即可；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>博尔安亲托管中心官方号</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>卖点=专业托管用心让家长放心 #作业辅导 #课后服务；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>壹心托管济南校区</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 12 条</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>粉丝=1797；卖点=爱有温度，行有尺度；心存敬畏，事求极致。壹心托管胜利大街校区正式启航；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv；主页=https://www.douyin.com/user/MS4wLjABAAAAaUBMtA-9SvagxcGJfXlgx1eQ3S1oGfkTKxnmmtUJdH8MPRQLIdeQwSV6JfHrTsaO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>大明湖的夏耦合</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>卖点=学校有配餐的建议二年级再去吃，小饭桌是刚需，但行业错综复杂。；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>天朗气清</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>卖点=#新学期 #托管 #一切为了孩子 #学习 #见证成长；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>天空教育官方号</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>账号；公开搜索结果账号</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>粉丝=855；卖点=济南市中区和槐荫区12年教培托管；午托、晚托、美术、书法；服务上万客户；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv；主页=https://www.douyin.com/user/MS4wLjABAAAAXB6u9Hfgy265b-Mn1mEsIIVncQ4_dyG7QwwDnkZFA4k8oZj5KjMFIr9tnef-3bwX</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>安馨托教｜西站路小学 52中午晚托</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>卖点=@安馨托教｜西站路小学 52中午晚托；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>小星星学堂【优优老师】</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>卖点=#实验中学 #实验托管 #托管日常；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>开托管的80后</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>卖点=托管招生 #托管；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>彩虹泡泡教育管家</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>卖点=济南儿童成长陪伴师 #济南 #儿童成长陪伴 #女性创业；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>悦维美刻托管济南站</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>卖点=像这样的品牌托管今年就会开在济南各个中学门口 #中学生托管中心 #济南中学生托管；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>成立志</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>卖点=志立成长中心开始招生；自理、自立，做真教育；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>新智托管</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>卖点=托管老师日常：接娃、维持秩序、订正错题，沉浸式辅导；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>李星野</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>卖点=用心、长久、安全；靠实打实的口碑积累记录托管校区成长；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>泉海托管</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>卖点=济南泉海学校附近专业托辅 #托管 #泉海学校 #素养课堂；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>济南书墨托管李老师</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>账号；公开搜索结果账号</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>粉丝=3741；卖点=20年儿童教育；中小学精品托管；辅导过济南中小学生；有温度的托管班；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv；主页=https://www.douyin.com/user/MS4wLjABAAAA-XE1-eX-ShMbHMdNFxFd9rBmyxb8UFySlyvYsFcyC7Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>济南书法飒老师</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>卖点=开学第一天 #新学期托管 #缘承托管 #专业晚辅 #济南托管 #西客站；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>济南卓安官方号</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>卖点=#济南托管 #小班托管 #济南同城 #卓安 #课后陪伴；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>济南卓阳优托</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>账号；公开搜索结果账号</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>粉丝=1306；卖点=天桥区老牌托管；专业师资；暖心托管；靠谱托管让家长安心；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv；主页=https://www.douyin.com/user/MS4wLjABAAAASnqzITf1VyCBa2Zt-mgaoo74JTZhRMAiU4ZJRv3aLisQNv22w9uf_T6HpiZuL1BM</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>济南天才自助餐托管中心</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>卖点=把饭做好，孩子吃饱，家长认可，这就是口碑 #托管用餐 #学生餐；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>济南学成课后中心</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>账号；公开搜索结果账号</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>粉丝=1109；卖点=在济南开托管10年的老托管人；两家校区，经五路+万科城；欢迎参观咨询；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv；主页=https://www.douyin.com/user/MS4wLjABAAAApCAPQqLg4mwNCO4t_btg-aiUQrs7ioXegGPVB0vyZ5o</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>济南市快乐助学坊成长中心～李老师</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 2 条</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>卖点=济南家长圈有口皆碑！19年0投诉托管班；接娃+辅导+晚餐全包 #济南托管 #快乐助学坊；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>济南市槐荫区惠心托管中心</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>粉丝=451；卖点=幼儿园园长转型；多年幼教管理；懂教育、懂孩子、重安全；800㎡空间；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv；主页=https://www.douyin.com/user/MS4wLjABAAAAWdUDcQpSeHIiHy_bMc9BwZSfsRjrQaxuhgvih2V3S4Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>济南慧学优安托</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>账号；公开搜索结果账号</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>粉丝=2135；卖点=高端托管；15年教育旅程；教育理念与托管日常；梦想乐园；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv；主页=https://www.douyin.com/user/MS4wLjABAAAAM2VEn5oqax3vnF-X5IwPw3smJq6p-MZ-o4l85pRh4Pp8cWyB9FDqPynHIeJtIwyI</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>济南托管王校长</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>账号；公开搜索结果账号</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>粉丝=1854；卖点=教育从业20年；专业晚辅、培优、午餐午休；从小托管做成百人大校；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv；主页=https://www.douyin.com/user/MS4wLjABAAAAVt6NUO0w1inbThSBgrXFgWmgQNMAMm2EDy2CASLfO-E</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>济南托管郑老师</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>卖点=#济南 #济南托管 #济南托管郑老师 #济南托管哪家好？ 来看看投资400万托管的秘密吧；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>济南托管高老师</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>账号；公开搜索结果账号</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>粉丝=2096；卖点=十几年经验；小学生午托、晚托；习惯培养，不只接送、吃饭、写作业；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv；主页=https://www.douyin.com/user/MS4wLjABAAAAIYA9gydLiokUYk3crHxZ2YAhhh7ewb0WkYC23gR4gZo</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>济南无忧托管</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>账号；公开搜索结果账号</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>粉丝=152；卖点=托您所爱、管您所忧；胜利大街小学托管；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv；主页=https://www.douyin.com/user/MS4wLjABAAAAvmz3VbMJzu2DRKl8OecxleSbqSjlnDL1AHdLw67dLxM</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>济南杨柳春风（正信置业）</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 2 条</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>卖点=#小春风播报 #名校；学校师资水平介绍；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>济南槐荫123托管成长中心</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>账号；公开搜索结果账号</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>粉丝=0；卖点=8年小学托管；作业辅导、安全接送、营养晚餐、书法/阅读作文/英语启蒙；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv；主页=https://www.douyin.com/user/MS4wLjABAAAAVEn7Mb8t2LbYbQ2XMsDXYbOtVqM6uIGEdX1hTCzzeZ9sF3SCZYh8-XTVlkdeKTU3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>济南槐荫小火竹官方号</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 4 条</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>粉丝=350；卖点=00后美院本科生，四年托管经验，23岁孤注一掷，耗资百万打造槐荫托管天花板！#高端托管中心 #小学生托管 #作业辅导托管；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv；主页=https://www.douyin.com/user/MS4wLjABAAAAH3zONTSzG-Yo8-aLh505CHGPCjQ44e6T_8Q8vtbdbHffbHdReSXOvN7aCEXuBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>济南槐荫顺馨教育</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>账号；公开搜索结果账号</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>粉丝=477；卖点=午餐午休、晚托作业、习惯养成、周末/假期托管；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv；主页=https://www.douyin.com/user/MS4wLjABAAAAlHNe8n-9xHljuFjafYgSaoFNlWudMuYbIYEXVVCPHMs</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>济南老董</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>卖点=上小学了要不要报小饭桌？家长经验分享 #济南小学 #济南小饭桌；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>济南蜗牛等等托育服务有限公司</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>账号；公开搜索结果账号</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>粉丝=2117；卖点=济南托育示范点；自然教育；招生0-4岁；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv；主页=https://www.douyin.com/user/MS4wLjABAAAAx9hspCfPAWOr_cphRDSG9euBmHM_IAgEr8iabDWpv7AbgwPHaeSuQdx_GjNhyMXa</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>省实验校内王老师</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 2 条</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>卖点=开学了！#济南 #小饭桌 #日常 #vlog；近30日估计=2</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>章丘托管金八力刘笑</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>卖点=退让换来的是无底线的伤害，这次我一定刚到底！#章丘托管 #章丘托管班；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>精心托管槐荫区医学中心小学宸园北区12号</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 2 条</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>卖点=精心托管新校区已规整完毕，地址：宸园北区12-2-101，静候小朋友归来；近30日估计=2</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>美吉精品托管</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>卖点=七里河区西站美吉精品托管火热招生中；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>老谢家的二姑娘</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>卖点=一日托管流程，期待更多的宝贝加入我们 #托管；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>花锦时代</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>粉丝=1；卖点=槐荫实验学校附近晚辅：20人以下小班、作业全查、错题精讲、接送方便、健康晚餐；原价880元/月，前10名首月减100元，39.9元体验3天含晚餐；公开价格=880元/月；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv；主页=https://www.douyin.com/user/MS4wLjABAAAAPJ3lf0Jz5HvHFxnqgUtQkrwjiIGy7VyZ8DqxCHK6gjeHBgWjC_IgmDr3PMkR1Qzq</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>萌雅童乐托管</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>粉丝=234；卖点=原槐荫区营市街幼儿园；普惠、传统文化、鼓乐、书法、棋类等；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv；主页=https://www.douyin.com/user/MS4wLjABAAAAGhzQAX8Wg_JxYiCpwrDq2J01qUtQjHFgtCQtHAh5TpPfZGu35AL3KWgCMKZSkiwG</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>营东小学天天托管来啦</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 2 条</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>卖点=#新学期新开始 #托管 招生啦；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>诺德城依春然托管</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>卖点=关于依春然；托管班、小饭桌、小学；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>贝尔优能任兴校区</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>卖点=实验学校附近报托管就找王老师；专业、更靠谱；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>贝尔安亲课后托管加盟</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>卖点=实地探访，学期收费17800元的托管；托管收费与餐食探店；公开价格=17800元；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>郑老师教育</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>账号；公开搜索结果账号</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>粉丝=6191；卖点=30+分校；分享幼升小、小升初、中高考择校规划、政策解读、真题干货；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv；主页=https://www.douyin.com/user/MS4wLjABAAAAdArEeYtGLBCQbbkSqrb0f3Y1yA9oXFc9VNsxCSjRzYynuKGtkqvsk8zauvz-fK8S</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>长清恒大育贤博跃托管—李老师</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>卖点=好的习惯在日复一日的陪伴中悄然生根；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>长清黑美人</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>卖点=长清一家做的非常好的托管，济南的都过来学习交流！#托管 #长清托管；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>静慧托管～雪婷</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>卖点=晚辅但不是普通晚辅；标准化流程、个性化一对一辅导；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>龙兴之家 课后伴学</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>粉丝=18；卖点=泉景小学对门托管；每日新鲜食材，荤素均衡搭配；龙兴之家课后伴学；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv；主页=https://www.douyin.com/user/MS4wLjABAAAAE5vr1pF_dwIVY_z7c8rmU50N5jVwmhyfXn50od8SM4i2PFlOFNZMLNWF8vAfXGFd</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>龚老师和她的托管朋友</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>卖点=和托管老师闹过别扭，换了几家对比后觉得这家靠谱；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ꕥ多财💞多亿</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 2 条</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>卖点=泉景小学附近新开托管，做接校、托管、寒暑假、餐食和作业反馈 #泉景小学 #卧龙花园；近30日估计=0</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>🌈俊霖托管🌈</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>卖点=关于秋季晚辅，随便问 #秋季晚辅 #小学 #初中；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>💕济南武老师教育精品一站式托辅✨</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>账号；公开主页；采样帖子 1 条</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>卖点=#营市东街 做一家让家长认可省心的托管机构；近30日估计=1</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/accounts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>帖子｜济南托管郑老师</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>帖子；2025年1月17日</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>赞=42；时长=01:32；#济南 #济南托管 #济南托管郑老师 #济南托管哪家好？ 来看看投资400万托管的秘密吧</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>帖子｜济南市快乐助学坊成长中心～李老师</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>帖子；2025年3月20日</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>赞=93；时长=01:41；济南家长圈有口皆碑！19年0投诉托管班；接娃+辅导+晚餐全包 #济南托管 #快乐助学坊</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>帖子｜壹心托管济南校区</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>帖子；6月29日</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>赞=10；时长=00:50；爱有温度，行有尺度；心存敬畏，事求极致。壹心托管胜利大街校区正式启航</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>帖子｜章丘托管金八力刘笑</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>帖子；8月25日</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>赞=456；时长=02:26；退让换来的是无底线的伤害，这次我一定刚到底！#章丘托管 #章丘托管班</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>帖子｜济南槐荫小火竹官方号</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>帖子；5月13日</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>赞=98；时长=00:54；00后美院本科生，四年托管经验，23岁孤注一掷，耗资百万打造槐荫托管天花板！#高端托管中心 #小学生托管 #作业辅导托管</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>帖子｜长清黑美人</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>帖子；8月30日</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>赞=240；时长=03:31；长清一家做的非常好的托管，济南的都过来学习交流！#托管 #长清托管</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>帖子｜省实验校内王老师</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>帖子；8月22日</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>赞=39；时长=01:28；开学了！#济南 #小饭桌 #日常 #vlog</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>帖子｜彩虹泡泡教育管家</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>帖子；2025年3月13日</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>赞=48；时长=02:31；济南儿童成长陪伴师 #济南 #儿童成长陪伴 #女性创业</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>帖子｜悦维美刻托管济南站</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>帖子；2025年5月2日</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>赞=20；时长=00:54；像这样的品牌托管今年就会开在济南各个中学门口 #中学生托管中心 #济南中学生托管</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>帖子｜济南槐荫小火竹官方号</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>帖子；5月13日</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>赞=98；时长=00:54；00后美院本科生，四年托管经验，耗资百万打造槐荫托管天花板！#高端托管中心 #小学生托管 #作业辅导托管</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>帖子｜🌈俊霖托管🌈</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>帖子；8月20日</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>赞=2；时长=00:29；关于秋季晚辅，随便问 #秋季晚辅 #小学 #初中</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>帖子｜济南市槐荫区惠心托管中心</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>帖子；13小时前</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>赞=6；时长=00:55；一晃十五年过去了，这段时光里有收获，也有遗憾。</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>帖子｜开托管的80后</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>帖子；3月4日</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>赞=8；时长=图文；托管招生 #托管</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>帖子｜精心托管槐荫区医学中心小学宸园北区12号</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>帖子；8月27日</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>赞=2；时长=图文；精心托管新校区已规整完毕，地址：宸园北区12-2-101，静候小朋友归来</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>帖子｜精心托管槐荫区医学中心小学宸园北区12号</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>帖子；6天前</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>赞=6；时长=图文；教师节到了，送给一线老师们，细心用心教育陪伴孩子</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>帖子｜济南卓安官方号</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>帖子；1天前</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>赞=9；时长=00:32；#济南托管 #小班托管 #济南同城 #卓安 #课后陪伴</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>帖子｜济南槐荫小火竹官方号</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>帖子；7月28日</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>赞=18；时长=00:33；高投入的托管中心，哪里区别于普通小饭桌？#槐荫区托管 #小火竹托管</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>帖子｜大明湖的夏耦合</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>帖子；2021年5月30日</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>赞=1164；时长=01:06；学校有配餐的建议二年级再去吃，小饭桌是刚需，但行业错综复杂。</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>帖子｜省实验校内王老师</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>帖子；7月25日</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>赞=38；时长=01:25；沉浸式体验高中小饭桌做饭的一天 #日常 #vlog #济南</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>帖子｜壹心托管济南校区</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>帖子；2025年9月15日</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>赞=22；时长=00:18；百万级别小饭桌，都给孩子们吃什么？带大家看一看</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>帖子｜壹心托管济南校区</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>帖子；2025年11月23日</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>赞=166；时长=00:16；与根posts.csv post_id=7575856001335147953匹配，未重复追加；托管天花板，神仙小饭桌，就是这么硬核 #济南壹心托管</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>帖子｜济南老董</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>帖子；6月18日</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>赞=33；时长=03:00；上小学了要不要报小饭桌？家长经验分享 #济南小学 #济南小饭桌</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>帖子｜济南天才自助餐托管中心</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>帖子；6月3日</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>赞=14；时长=02:16；把饭做好，孩子吃饱，家长认可，这就是口碑 #托管用餐 #学生餐</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>帖子｜天朗气清</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>帖子；2025年8月22日</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>赞=4；时长=01:28；#新学期 #托管 #一切为了孩子 #学习 #见证成长</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>帖子｜ꕥ多财💞多亿</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>帖子；6月23日</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>赞=5；时长=图文；泉景小学附近新开托管，做接校、托管、寒暑假、餐食和作业反馈 #泉景小学 #卧龙花园</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>帖子｜龙兴之家 课后伴学</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>帖子；3天前</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>赞=9；时长=图文；泉景小学对门托管；每日新鲜食材，荤素均衡搭配；龙兴之家课后伴学</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>帖子｜ꕥ多财💞多亿</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>帖子；6月18日</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>赞=5；时长=00:20；泉景中学对面19号楼托管开业，幼小衔接，一二年级 #卧龙花园 #泉景中学</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>帖子｜济南市快乐助学坊成长中心～李老师</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>帖子；2025年3月20日</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>赞=93；时长=01:41；济南家长圈有口皆碑！19年0投诉；接娃+辅导+晚餐全包</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>帖子｜壹心托管济南校区</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>帖子；2025年7月26日</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>赞=15；时长=00:32；托管天花板，神仙小饭桌，吃货娃挑食娃都来做壹心的娃 #泉海学校</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>帖子｜努力的龙</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>帖子；8月5日</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>赞=102；时长=01:14；谁家托管点100杯果汁啊 #托管班 #托管上班日常</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>帖子｜济南书法飒老师</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>帖子；9月1日</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>赞=10；时长=00:12；开学第一天 #新学期托管 #缘承托管 #专业晚辅 #济南托管 #西客站</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>帖子｜六六托管中心闫老师🙋（高端，专业）</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>帖子；3月7日</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>赞=17；时长=03:39；#托管 #济南；一心只做托管，用心用爱撑起托管的孩子！</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>帖子｜安馨托教｜西站路小学 52中午晚托</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>帖子；8月21日</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>赞=14；时长=00:09；@安馨托教｜西站路小学 52中午晚托</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>帖子｜美吉精品托管</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>帖子；2025年8月22日</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>赞=17；时长=01:01；七里河区西站美吉精品托管火热招生中</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>帖子｜贝尔安亲课后托管加盟</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>帖子；3月20日</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>赞=251；时长=03:45；公开价格=17800元；实地探访，学期收费17800元的托管；托管收费与餐食探店</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>帖子｜💕济南武老师教育精品一站式托辅✨</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>帖子；8月29日</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>赞=11；时长=00:23；#营市东街 做一家让家长认可省心的托管机构</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>帖子｜营东小学天天托管来啦</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>帖子；2024年8月30日</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>赞=5；时长=00:30；#新学期新开始 #托管 招生啦</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>帖子｜萌雅童乐托管</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>帖子；2022年8月2日</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>赞=26；时长=02:44；营市街幼儿园位于营市东街44号；普惠性幼儿园，传统文化、鼓乐、书法、棋类等特色课程</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>帖子｜李星野</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>帖子；7月23日</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>赞=149；时长=00:59；用心、长久、安全；靠实打实的口碑积累记录托管校区成长</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>帖子｜老谢家的二姑娘</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>帖子；8月23日</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>赞=36；时长=01:20；一日托管流程，期待更多的宝贝加入我们 #托管</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>帖子｜东街小学欣悦托辅</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>帖子；8月31日</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>赞=27；时长=02:43；托管班大门已敞开，等待热爱学习的小小探索者 #开学季 #招生季</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>帖子｜营东小学天天托管来啦</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>帖子；2024年7月10日</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>赞=4；时长=00:15；下午数学课学习；理论与实践结合 #营市东街小学 #天天托管</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>帖子｜花锦时代</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>帖子；8月22日</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>赞=0；时长=图文；公开价格=880元/月；槐荫实验学校附近晚辅：20人以下小班、作业全查、错题精讲、接送方便、健康晚餐；原价880元/月，前10名首月减100元，39.9元体验3天含晚餐</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>帖子｜贝尔优能任兴校区</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>帖子；3月20日</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>赞=50；时长=00:33；实验学校附近报托管就找王老师；专业、更靠谱</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>帖子｜小星星学堂【优优老师】</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>帖子；4月22日</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>赞=11；时长=00:22；#实验中学 #实验托管 #托管日常</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>帖子｜壹心托管济南校区</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>帖子；2025年6月26日</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>赞=37；时长=03:19；与根posts.csv post_id=7520469530099993914匹配，未重复追加；校区从市场调研到落地成型；记录建设过程 #高端托管 #泉海中学</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>帖子｜济南槐荫小火竹官方号</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>帖子；7月28日</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>赞=6；时长=00:53；高投入的托管中心，哪里区别于普通小饭桌？</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>帖子｜万小妹</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>帖子；5月18日</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>赞=61；时长=02:56；济南最美学校，绿城育华杨柳春风学校食堂；一蔬一饭藏教养</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>帖子｜济南杨柳春风（正信置业）</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>帖子；2021年11月1日</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>赞=344；时长=01:27；#小春风播报 #名校；学校师资水平介绍</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>帖子｜龚老师和她的托管朋友</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>帖子；6月16日</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>赞=286；时长=00:08；和托管老师闹过别扭，换了几家对比后觉得这家靠谱</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>帖子｜十七小学繁星托管</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>帖子；2天前</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>赞=14；时长=00:31；开学两个星期了；做托管的是良心，尽心即可</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>帖子｜诺德城依春然托管</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>帖子；2025年8月16日</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>时长=关于依春然；关于依春然；托管班、小饭桌、小学</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>帖子｜济南杨柳春风（正信置业）</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>帖子；2022年3月1日</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>赞=105；时长=05:46；绿城育华杨柳春风幼儿园云参观 #济南</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>帖子｜长清恒大育贤博跃托管—李老师</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>帖子；16小时前</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>赞=6；时长=01:49；好的习惯在日复一日的陪伴中悄然生根</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>帖子｜壹心托管济南校区</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>帖子；2025年8月21日</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>赞=25；时长=02:04；什么情况啊来了就不想走的托管见过么 #济南壹心托管</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>帖子｜壹心托管济南校区</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>帖子；2025年7月5日</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>赞=7；时长=01:39；市中区泉海学校对面开了一家星级托管，出校门步行一分钟</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>帖子｜壹心托管济南校区</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>帖子；2025年7月24日</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>赞=13；时长=00:36；做托管要站在家长角度，用真心换放心</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>帖子｜新智托管</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>帖子；1天前</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>赞=23；时长=04:57；托管老师日常：接娃、维持秩序、订正错题，沉浸式辅导</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>帖子｜静慧托管～雪婷</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>帖子；6月24日</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>时长=晚辅标准化；晚辅但不是普通晚辅；标准化流程、个性化一对一辅导</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>帖子｜成立志</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>帖子；8月23日</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>赞=49；时长=00:38；志立成长中心开始招生；自理、自立，做真教育</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>帖子｜乐思托辅</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>帖子；7月3日</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>赞=6；时长=00:32；实验中学校区托管，只有12个床位，招满即可</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>帖子｜壹心托管济南校区</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>帖子；2025年7月11日</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>赞=48；时长=00:42；与根posts.csv post_id=7525763465560313146匹配，未重复追加；壹心只做一件事，用心做好一件事；托管正式启航</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>帖子｜94年小王｜盘锦初中晚自习托管</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>帖子；8月14日</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>赞=3；时长=01:16；实验中学新初一家长注意；爱顿校区安可托管中心环境展示</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>帖子｜云朵中心</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>帖子；8月31日</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>赞=83；时长=04:37；开学前一天校区安全、卫生标准讲解</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>帖子｜博尔安亲托管中心官方号</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>帖子；2023年4月8日</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>赞=8；时长=02:35；专业托管用心让家长放心 #作业辅导 #课后服务</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>帖子｜壹心托管济南校区</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>帖子；2025年10月14日</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>赞=19；时长=00:33；上学的孩子拼脑力也是拼体力，为泉海校区娃娃成长助力，用心做好每一餐</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>帖子｜壹心托管济南校区</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>帖子；2025年12月20日</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>赞=15；时长=00:29；这里是济南壹心托管泉海校区；很高兴认识你</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>帖子｜泉海托管</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>帖子；3月21日</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>赞=3；时长=00:29；济南泉海学校附近专业托辅 #托管 #泉海学校 #素养课堂</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>帖子｜乐恩托管</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>帖子；5小时前</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>赞=0；时长=00:17；每一刻都值得被记录 #泉海学校 #乐恩托管 #晚辅日常</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>帖子｜壹心托管济南校区</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>douyin</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>帖子；2025年8月5日</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>赞=12；时长=00:28；想要了解的过来看看吧 #每日分享</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>02_douyin_competitors/posts.csv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
+  <autoFilter ref="A1:E133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/research/jinan_tuoguan_2026/济南托管调研_v1.xlsx
+++ b/research/jinan_tuoguan_2026/济南托管调研_v1.xlsx
@@ -22,12 +22,12 @@
     <sheet name="任务1_抽取字段" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'任务1_抖音竞品'!$A$1:$W$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'任务1_抖音竞品'!$A$1:$X$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'任务2_点评美团'!$A$1:$H$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'任务3_地图POI'!$A$1:$Q$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'任务4_企查查'!$A$1:$H$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'任务5_政府政策'!$A$1:$H$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'任务6_小红书'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'任务6_小红书'!$A$1:$N$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'任务7_抖音同城'!$A$1:$E$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'任务8_场地租金'!$A$1:$F$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'任务9_人工成本'!$A$1:$E$17</definedName>
@@ -56,7 +56,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +66,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004F81BD"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -102,6 +107,9 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -180,7 +188,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T1" displayName="T1" ref="A1:Q21" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T1" displayName="T1" ref="A1:X19" headerRowCount="1">
   <autoFilter ref="A1:Q21"/>
   <tableColumns count="17">
     <tableColumn id="1" name="platform"/>
@@ -642,7 +650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -668,6 +676,7 @@
     <col width="20" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="40" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -786,6 +795,11 @@
           <t>comment_negative</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>asr_path</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -879,6 +893,11 @@
       <c r="W2" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>06_transcripts/7677935290225392369.txt</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -972,6 +991,11 @@
       <c r="W3" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>06_transcripts/7575856001335147953.txt</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1065,6 +1089,11 @@
       <c r="W4" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>06_transcripts/7637491112080667633.txt</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1158,6 +1187,7 @@
       <c r="W5" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="X5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1247,6 +1277,11 @@
       <c r="W6" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>06_transcripts/7525763465560313146.txt</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1340,6 +1375,7 @@
       <c r="W7" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="X7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1433,6 +1469,11 @@
       <c r="W8" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>06_transcripts/7653846998802236337.txt</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1526,6 +1567,7 @@
       <c r="W9" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="X9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1619,6 +1661,11 @@
       <c r="W10" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>06_transcripts/7678673116122259579.txt</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1712,6 +1759,11 @@
       <c r="W11" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>06_transcripts/7527685990393400634.txt</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1805,6 +1857,7 @@
       <c r="W12" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="X12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1896,6 +1949,7 @@
       <c r="W13" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="X13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1988,6 +2042,11 @@
       </c>
       <c r="W14" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>06_transcripts/7682957097429101681.txt</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -2078,6 +2137,7 @@
       <c r="W15" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="X15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2171,6 +2231,7 @@
       <c r="W16" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="X16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2264,6 +2325,7 @@
       <c r="W17" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="X17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2357,6 +2419,11 @@
       <c r="W18" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>06_transcripts/7675698430941783409.txt</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2450,9 +2517,14 @@
       <c r="W19" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>06_transcripts/7675336617532168185.txt</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W19"/>
+  <autoFilter ref="A1:X19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -11539,45 +11611,6410 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:N113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>关键词</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>平台</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>结果</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>证据路径</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>record_type</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>note_id</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>comment_id</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>author</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>likes</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>comments_count</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>published_at</t>
+        </is>
+      </c>
+      <c r="L1" s="6" t="inlineStr">
+        <is>
+          <t>source_keyword</t>
+        </is>
+      </c>
+      <c r="M1" s="6" t="inlineStr">
+        <is>
+          <t>collected_at</t>
+        </is>
+      </c>
+      <c r="N1" s="6" t="inlineStr">
+        <is>
+          <t>evidence_path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6aa91819000000000d026b80</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>济南宝妈分享｜靠谱托管，真的能减轻不少</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>托管日常，不只是盯着写作业而已。辅导作业前老师会提前做习题，梳理重难点和易错点；空余时间陪孩子做手抄报；对磨蹭的孩子用计时器训练时间观念。教师节收到家长小蛋糕。面向鑫苑世家、西城实验小学周边。
+【标注】正向：作业辅导、习惯训练、家长认可；未披露价格。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>家长A</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6aa91819000000000d026b80?xsec_token=ABNpEzSkABPr3gk1bnc4ACCutEHApup7G-7PVTFT8AAKE=&amp;xsec_source=pc_search</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>20小时前</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>济南托管</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>69fee543000000002202bb05</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>在济南｜有一家很棒的托管</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>宣传干净舒适、分区管理，提供阅读和自习空间；每日现做营养餐；阅读、体能活动；强调安全、安心、舒心成长。账号为恐龙童成儿童成长中心，评论回复位置在奥体中心、全运村。
+【标注】被赞：环境、餐食、分区管理；组织：恐龙童成儿童成长中心；未披露价格。</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>恐龙童成儿童成长中心</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fee543000000002202bb05?xsec_token=ABxGZ1j-aTsUtrx0xUsH4VDE3NZfTrOupgdj52HdXo_x4=&amp;xsec_source=pc_search</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>05-10</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>济南托管</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6a8d6eeb000000001803c15e</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>山东校外托管服务规范提示｜9月16实施</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>解读山东省《关于加强校外托管机构监管的意见》（2026-09-16施行）：营利性需营业执照，餐饮需食品许可/小餐饮登记，从业人员健康证；禁地下室、半地下室、危房、低等级夹芯板，与易燃易爆场所同楼；托管不得变相学科培训或作业辅导；教育、公安、市场监管、消防联合监管，12345举报即核查；家长互助托管5人内非盈利不受商业约束。作者判断住宅小饭桌合规/消防难，成本和收费或上涨。
+【标注】痛点：消防、餐饮资质、合规成本；可能影响济南住宅小饭桌。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>归舍空间设计</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6a8d6eeb000000001803c15e?xsec_token=AB1OD-byM-SwOWLUI5eJRf2DoH8T0fmTPMhL2pK3mHmFU=&amp;xsec_source=pc_search</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>编辑于 08-25</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>济南托管</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>69d71f32000000001a02a86e</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>济南贝尔安亲托管！高端托管大揭秘</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>贝尔安亲济南舜华校区宣传：持证/培训师资、小班陪护、同步校内知识点；新鲜食材、忌口安排、独立休息区一人一床、消杀通风、监控反馈；引导式作业辅导和习惯培养，多校区。
+【标注】被赞：师资、餐食安全、休息区、反馈；组织：贝尔安亲济南舜华校区；未披露价格。</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>多翊｜贝尔安亲济南舜华校区</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69d71f32000000001a02a86e?xsec_token=AB1Zw-wwKplherrEhORytrNf4DrRwcajZVv7rnqJPTLwg=&amp;xsec_source=pc_search</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>编辑于 04-20</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>济南托管</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6a6c41290000000028007273</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>济南上班族狂喜｜5-6岁整周托管终于找到了</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>济南学易佳面向5-6岁，周一至周五全天「一周适应体验课」，5天¥199；作息、午休、课堂规则、社交、自理训练，老师记录适应表现。
+【标注】价格：199元/5天；组织：济南学易佳；适合幼升小/幼儿托管。</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>济南学易佳</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6a6c41290000000028007273?xsec_token=AB0pGdJHjj5HHePofKgwIUFhQ6QxpYs8A1nu65DPxcqHY=&amp;xsec_source=pc_search</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>07-30</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>济南托管</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6aa37734000000000b00d2a8</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>挖到宝！这家托管也太香了！</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>一名成长中心宣传跟学托管营养餐：孜然鸡丁、炸蘑菇、菠菜、白菜炖豆腐、小米南瓜粥、馒头等，强调蛋白、蔬菜、养胃和不重样。
+【标注】被赞：餐食搭配、营养、多样；组织：一名成长中心；未披露价格。</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>一名成长中心</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6aa37734000000000b00d2a8?xsec_token=AB4u-bXe4QZjPERDEZX4MVpsfftBFLuhja9tLhIeu2jX8=&amp;xsec_source=pc_search</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>5天前</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>济南托管</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>济南求职避雷｜该历城托管真的太离谱了❌</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>求职者称历城某托管面试/入职不提前说规则，实习两天不给工资；隐形工作、无偿打扫卫生、接孩子放学久等，早六晚七且工资低。评论提到试岗无薪、教师资质/法律维权疑问，并有评论指向“wutongtuoguan”、疑似“萌芽”（均为评论信息，未独立核实）。
+【标注】痛点：试岗/拖欠工资、隐形劳动、超长工时；组织/名称：wutongtuoguan（评论指称）。</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>家长B</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6a068d7a00000000350229b4?xsec_token=AB6wmZbQex5cbnZ9Q8B2PQXNPy4ixI0n2svFY4YkFwsRg=&amp;xsec_source=</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>05-14</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>济南托管避雷</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6a659e810000000004029ccf</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>避雷济南历城区托管 欠工资</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>作者称历城区某托管拖欠工资，评论问是否还找工作、欠多少，并出现“张马屯这个？”等线索，未披露机构全名。
+【标注】痛点：欠工资；机构身份未核实。</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>家长C</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6a659e810000000004029ccf?xsec_token=ABEUqrjd5JhFQLnVBUnSNmXpGfFsu2oierbpGifArUEC4=&amp;xsec_source=</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>07-25</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>济南托管避雷</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6a8a7111000000002802e94b</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>济南槐荫区实验学校晚辅招学生啦</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>槐荫区实验学校附近晚辅：20人以下小班、作业全查错题精讲、习惯培养、离学校近接送方便、健康晚餐。原价880元/月；前10名首月减100元；39.9元体验3天晚辅（含晚餐）；三人同行每人再减100元。地址称在槐荫区实验学校附近300米北京烤鸭二楼。
+【标注】价格：880元/月，体验39.9元/3天；组织/地点：槐荫区实验学校附近。</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>优秀的小福宝</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6a8a7111000000002802e94b?xsec_token=ABrnFEseFGcQFfvkxrPaqlQMltTK_5NsnFK2PjzX5iSAc=&amp;xsec_source=</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>编辑于 08-22</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>槐荫托管</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6a824f6e0000000033013513</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>泉景小学附近小饭桌，求推荐！</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>一年级新生家长求推荐泉景小学附近靠谱小饭桌；后续作者回复已找到附近幼儿园托管。评论提到“绿沅幼儿园”、博雅幼儿园满员、22号楼那家老师负责等线索，均为评论信息未独立核实。
+【标注】需求：泉景小学一年级；线索：绿沅幼儿园/附近幼儿园托管；价格未披露。</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>家长D</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6a824f6e0000000033013513?xsec_token=AB_Gs2xf2j74kekdsRt7XgUMipEaK1OlvtIeklqs2kSkE=&amp;xsec_source=</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>08-16</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>泉景托管</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>673098bd000000001a01dd9c</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>泉景中学小饭桌，源于一个妈妈对孩子的爱💖</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>泉景中学小饭桌，文案强调妈妈陪伴；餐食视频/图片。评论问最晚到几点，作者回复“一般六点”；另有评论问收费但未见回复。
+【标注】时间：一般六点；价格未披露；账号“蛋仔妈咪666”疑似家长/经营者，未核实。</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>家长E</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/673098bd000000001a01dd9c?xsec_token=AB5F-Grkcio8dZYT9GPeagXUHp0mOaHKYZ-4xsjHakau0=&amp;xsec_source=pc_search</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>泉景托管</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>673bfbe2000000000702a37c</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>济南泉景中学小学部附近小饭桌</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>泉景中学小学部附近小饭桌，展示周二餐食（视频/图片），未披露机构名、时间或价格。
+【标注】评论主要询问具体价格和时间；未披露。</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>家长E</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/673bfbe2000000000702a37c?xsec_token=ABJ08ezIZ47pGbgjW8KRliEihcKcLgyciaRUVsCN-Q3jc=&amp;xsec_source=</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>泉景托管</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>真的不建议送孩子去晚托班</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>作者认为晚托可能让孩子学会“应付”而非自主学习，建议家长关注自主规划、时间管理和主动思考，但承认并非适合所有家庭。高互动评论提供两类经验：有机构认真检查作业、读背默、查漏补缺并包吃，4点多到9点多，月600-800元/学期2500-3400元；也有评论称某些班学习环境差、无教师资质、照答案、饭量不足、管理混乱。
+【标注】痛点/分歧：托管质量差异、辅导边界、餐食、管理；价格样本：600-800元/月、2500-3400元/学期（评论，非济南本地，未核实）。</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>家长F</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69aa9417000000001d02762a?xsec_token=ABz9ApPhsfSSjooQgwCivjiloBlgIkuq4UXz4y38lz7pY=&amp;xsec_source=pc_search</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>03-06</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>杨柳春风学校托管</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>避雷托管</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>求职者称托管工作下午三点到机构、学生近六点放学，仍要求备课；每周五天、每天至少五小时、月1500-2500元、一人带十名学生。二编称低时薪却要求备课和负责到底，认为应至少4000元。评论另提臻源托管拖欠工资、试岗/工作强度、4点到8点时薪20元不管饭等。
+【标注】痛点：低薪、备课/卫生等隐形劳动、超长工时；评论提及组织“臻源托管”（未独立核实）。</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>elision</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69ff27630000000037034fca?xsec_token=ABtsoiy3Y_ZTHoIm6BrFJH3J4pbPIjsVYUs-dU2nDGS6o=&amp;xsec_source=pc_search</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>编辑于 05-09</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>杨柳春风学校托管</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>请教济南小学家长！现在济南小饭桌一月多少钱？没看到几个笔记讨论呢</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>济南小饭桌价格讨论：午餐750/月、午餐+晚餐1100/月；槐荫约900/月（午餐三菜一汤、下午粥和面包、看作业）；历下学校配餐15元/天；午晚餐1680/月；午托450/月；市中区约860-890/月；历下午晚托1460/月；历城配餐15元/天，校外可平躺午托22元/次；领秀城下午托管约1500/月；午晚托2000多/月。
+【标注】价格样本来自评论、地区/服务不同不可直接比较；正向反馈：槐荫评论称餐食和老师负责。</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>济南美食情报局（李大猫）</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6a5ef485000000001b01c1ec?xsec_token=ABLlVozvt44_xjVxWulxqCD3BRad2E5XmQ5-5116vFlXY=&amp;xsec_source=pc_search</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>07-20</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>济南托管价格</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/posts.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>69fee543000000002202bb05</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>69fee543000000002202bb05_c001</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>济南哪里？</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>家长G</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>05-24山东</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>69fee543000000002202bb05</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>69fee543000000002202bb05_c002</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>在奥体中心、全运村。</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>恐龙童成儿童成长中心</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>05-24山东</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>69fee543000000002202bb05</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>69fee543000000002202bb05_c003</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>你好，老师，接赞助吗</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>家长H</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>05-11河北</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4_c004</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>这哪家啊</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>家长I</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>05-29山东</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4_c005</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>历城区的wutongtuoguan</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>lucky</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>06-02山东</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4_c006</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>我也在找托管，前两天试岗两天没有钱，发现太多隐形工作，早上十点到晚上九点，就休息一个小时左右，其他时间都在忙，马上跑路了</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>家长J</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>05-14山东</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4_c007</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>真得抓紧跑路，甚至我去的这个都没说试岗期的事儿</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>lucky</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>05-14山东</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4_c008</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>打举报电话啊一举报一个准</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>家长K</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>05-14山东</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4_c009</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>没用，尝试过了人家根本不怕，而且还没毕业的应届毕业生不管</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>lucky</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>05-14山东</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4_c010</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>都这样而且还有干三天不行就走一分钱没有的，美其名曰三天试用期，后来去了另一个我才知道人家试用期也有工资</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>家长L</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>05-14山东</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4_c011</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>法律规定试用期就应该有工资的，但是拿他们没办法</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>lucky</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>05-14山东</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4_c012</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>这好像是萌芽吧</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>家长I</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>05-29山东</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4_c013</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>哪家呀</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>家长M</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>05-15山东</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4_c014</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>避雷吧，我之前还好，当时试岗三天没工资</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>家长N</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>06-04山东</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4_c015</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>有没有奥体中路这边想干托管的我要离职 找个人接替我 招不到人老板不让走</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>家长O</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>09-04山东</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4_c016</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>我之前在济南西附近的一个辅导班兼职，一开始不说，还有两天就要去上班了，和我说要我干完一整个暑假再给我结算工资，大几千块钱呢，我害怕到时候拿不到钱我就跑路了</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>家长P</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>05-15山东</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4_c017</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>这种更是离谱</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>lucky</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>05-16山东</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>6a068d7a00000000350229b4_c018</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>说是让仲裁和起诉，对方就笃定为了这点钱费时间费钱不可能，故意钻法律空子，这种老板还没倒闭也真是神了</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>lucky</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>05-14山东</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>6a659e810000000004029ccf</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>6a659e810000000004029ccf_c019</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>你还要找托管工作嘛</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>家长Q</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>07-26山东</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>6a659e810000000004029ccf</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>6a659e810000000004029ccf_c020</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>还有吗</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>家长R</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>07-26山东</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>6a659e810000000004029ccf</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>6a659e810000000004029ccf_c021</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>找他去</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>家长S</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>07-26山东</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>6a659e810000000004029ccf</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>6a659e810000000004029ccf_c022</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>拖欠了你多少啊</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>家长T</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>07-26山东</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>6a659e810000000004029ccf</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>6a659e810000000004029ccf_c023</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>哈哈</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>家长U</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>07-25山东</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>6a659e810000000004029ccf</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>6a659e810000000004029ccf_c024</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>张马屯这个？</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>家长V</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>07-26山东</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>6a659e810000000004029ccf</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>6a659e810000000004029ccf_c025</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>打电话</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>家长S</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>07-26山东</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>6a8a7111000000002802e94b</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>6a8a7111000000002802e94b_c026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>你好，咨询一下怎么收费？</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>家长W</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>08-31山东</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>673098bd000000001a01dd9c</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>673098bd000000001a01dd9c_c027</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>晚上最晚到几点亲？</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>家长X</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2025-10-17山东</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>673098bd000000001a01dd9c</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>673098bd000000001a01dd9c_c028</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>一般六点</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>家长E</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2025-12-02山东</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>673098bd000000001a01dd9c</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>673098bd000000001a01dd9c_c029</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>怎么收费</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>家长Y</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2025-08-05山东</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>673bfbe2000000000702a37c</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>673bfbe2000000000702a37c_c030</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>您好，请问具体价格和时间</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>家长Z</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2025-09-08山东</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>673bfbe2000000000702a37c</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>673bfbe2000000000702a37c_c031</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>这是哪家</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>家长AA</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2025-08-09山东</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a_c032</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>自己有能耐就自己辅导咯，没人要求你要放晚托班，你自己又想不辅导，又怕晚托不行，反正我的晚托是每个老师都认真检查孩子的作业（当然一个老师看六七个孩子，免不了会出现发现不了的错误），除了作业，我们还要求孩子读背默，最后还会给孩子查漏补缺，做提高的练习，包吃，下课四点多到九点多，一个月600-800贵吗？一个学期2500-3400，都是辛苦钱</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>家长AB</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>03-10广东</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a_c033</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>还便宜 我们这里一个月晚托1600</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>家长AC</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>03-10陕西</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a_c034</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>礼貌问下，老人把孩子接回家，但是父母孩子上班7点左右才到家，那这空白的时间应该怎么规划……（老人没法辅导作业）</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>家长AD</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>06-28福建</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a_c035</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>去运动</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>家长AE</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>06-28湖南</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a_c036</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>只能说你运气不好，考察的时候没遇到好机构！因为好的托班除了辅导学生作业，检查改错，讲解错题之外！还要根据学生的作业情况进行以及每次测验情况有针对性的帮学生辅导及巩固他们不懂的知识点！简单来说就是还得让他们的成绩有提升！</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>家长AF</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>04-01云南</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a_c037</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>礼貌问问这么搞，给多少一小时</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>家长AG</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>04-01上海</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a_c038</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>我本来选好一个晚托班，说的我都焦虑了，我是双职工家庭，最快6点之前接回来，刚上小学几周都鸡飞狗跳的，练点字得墨迹一个小时，还得吃饭，还得出去玩，9点半左右就得睡觉，原来每晚讲故事，现在一点时间没有了。</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>家长AH</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>5小时前北京</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a_c039</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>我在托管本干了四天，真的不建议送孩子去，第一没有学习环境，乱糟糟的，第二老师也不是专业老师，都是找来的宝妈闲散失业人员并没有教师资质，有的题他们也不会更不用说讲解了，他们都是作业帮一批作业完事了，甚至于遇到更差的学生他们会拿答案给孩子们抄，第三，孩子们都吃不饱，他们为了减少成本做的饭几乎每天都不够的，孩子吃饭限量，好吃的孩子再去盛饭就不给了，第四孩子们来自什么样家庭的都有……</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>家长AI</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>03-10陕西</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a_c040</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>那是你那个晚托班</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>加贝托管</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>07-25浙江</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a_c041</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>能管作业和晚餐已经帮了很大的忙咯</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>家长AJ</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>03-09四川</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a_c042</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>检查和复盘，晚上回家可以再做</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>家长AK</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>03-09贵州</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a_c043</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>托管≠辅导班，虽然我也是家长，但是我也看不惯本来孩子就不聪明，还指望托管给辅导成学霸。我就指望孩子有人接送，吃好喝好休息好。</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>家长AL</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>03-11宁夏</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a_c044</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>透彻</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>家长AM</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>03-11浙江</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a_c045</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>我是开托管班的，一个月孩子成绩进步10-20分，估计我是唯一一个把合伙人干跑的托管班，都说我太负责了，不能量化，赚不到钱，上了托管，课也不用补了，现在托管班已经倒闭了</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>家长AN</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>03-14浙江</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a_c046</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>你可以一对4自己带，我相信在浙江只要成绩到位，2万一学期我都愿意交</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>家长AO</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>08-25浙江</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a_c047</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>放学后的三小时，前两个小时家长还在上班</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>家长AP</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>04-29江苏</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a_c048</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>不建议的可以辞职自己带，不然真没有哪个双职工可以3点不到就下班的</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>家长AQ</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>04-29江苏</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a_c049</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>老师松吧不行，老师管的严格呢，又有话说了</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>家长AR</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>03-11江苏</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>69aa9417000000001d02762a_c050</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>今天严了一个男孩，哭了。。晚上家长就说不来了，无奈，一个小时4个字，我实在夸不起来</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>家长AS</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>03-11江苏</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca_c051</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>臻源托管拖欠工资</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>家长AT</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>09-05山东</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca_c052</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>顶顶顶</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>elision</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>09-05河北</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca_c053</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>托管还要备课给我整笑了</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>家长AU</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1297</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>05-09河北</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca_c054</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>要的</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>43石外托管（小升初版）</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>05-09河北</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca_c055</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>这种托管不就是看孩子写作业 如果有不会的题教他们吗为什么要去那么早</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>家长AV</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>05-09河北</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca_c056</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>对呀，我不理解，还要备课，备什么课呀？</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>elision</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>05-09河北</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca_c057</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>我现在管七个，一个晚上才一百，真的廉价</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>家长AW</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>05-10广东</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca_c058</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>我才80</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>家长AX</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>05-10河南</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca_c059</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>我下个月就要去托管试岗了，试用期每个月2800，说辅导10个4-6年级的小朋友，每天早上九点到晚上九点</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>家长AY</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>05-12广东</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca_c060</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>哈哈哈哈托管班离职的告诉你，有些家长就是又舍不得花钱上补习班，又要求成绩进步的</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>家长AZ</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>05-12江西</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca_c061</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>我去面试，一个班十来个学生不同年级都有，辅导语数英全科作业，作业要百分百正确，还要打扫卫生，4点到8点，时薪20，不管饭</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>家长BA</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>05-12北京</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca_c062</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>我的妈，在北京，20???</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>家长BB</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>05-31山东</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca_c063</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>有教师资格证，并且能讲题还讲的特别好为啥干托管，做辅导班时间灵活工资高不好吗</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>家长BC</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>06-05陕西</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca_c064</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>唉，当时不太清楚托管这个行业，就只是想找一份离家近的兼职，这样的话比较好备考</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>elision</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>06-05河北</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca_c065</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>我家有个亲戚开了个托管机构，找几个大学生来看着小孩写作业，一个月好像两三千，也不要求备课。本来就钱少还要备课，那谁去</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>家长BD</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>05-09重庆</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca_c066</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>就是这个理儿，1500还要备课</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>elision</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>05-09河北</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca_c067</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>我们这边必须经验＋教资，不能当面搜答案，怕学生告诉家长听，每天搞卫生，星期一老板办公室教师大厅大扫除，成绩退步扣钱，底薪2500-2700左右</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>家长BE</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>05-14湖南</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca_c068</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>托管真的好便宜，我不太明白，明明靠脑子吃饭，怎么工资那么低</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>家长BF</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>05-09广东</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>69ff27630000000037034fca_c069</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>大头都让老板占了，实质和辅导班差不多吧，中间商赚差价</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>家长BG</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>05-09江苏</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec_c070</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>我们午餐750，一个月1100。在开学我就不上班全职带他了</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>家长BH</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>07-20山东</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec_c071</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>合适</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>济南美食情报局（李大猫）</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>07-21山东</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec_c072</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>区域不一样吧，槐荫900，中午吃一顿三菜一汤，下午放学有粥和面包，看着写完作业检查完家长接，周五晚上不写完作业家长不允许接，我觉得非常好，老师很负责</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>家长BI</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>07-29山东</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec_c073</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>感谢分享</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>济南美食情报局（李大猫）</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>07-29山东</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec_c074</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>历下小学午餐是15一天，校外小饭桌不清楚</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>家长BJ</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>07-21山东</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec_c075</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>学校这个价格，性价比无敌</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>济南美食情报局（李大猫）</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>07-21山东</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec_c076</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>中午＋晚上，一个月1680</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>家长BK</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>07-22山东</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec_c077</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>中位数高一点点，高新或历下吗</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>济南美食情报局（李大猫）</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>07-22山东</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec_c078</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>只报名了午托，午餐加午休，450一个月</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>家长BL</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>07-27山东</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec_c079</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>哪里这么便宜，市中区大部分860 890</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>家长BM</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>08-29山东</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec_c080</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>中午在学校吃配餐，15元/天，中午趴桌子上睡。不过我家俩都说学校的配餐好吃</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>家长BN</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>07-21山东</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec_c081</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>那就行</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>济南美食情报局（李大猫）</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>07-21山东</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec_c082</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>历下一个月1460，午托和晚托</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>家长BO</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>07-23山东</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec_c083</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>晚托到几点呀</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>家长BP</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>07-23山东</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec_c084</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>历城，学校配餐15，校外能平躺睡觉的午托是22</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>家长BQ</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>07-22山东</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec_c085</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>中午平躺睡觉挺好</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>济南美食情报局（李大猫）</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>07-22山东</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec_c086</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>领秀城，100块钱一天；托管小饭桌加下午的话1500左右一个月</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>家长BR</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>07-21山东</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec_c087</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>午➕晚2000多</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>家长BS</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>07-20山东</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>6a5ef485000000001b01c1ec_c088</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>核心学区价格，有点硬</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>济南美食情报局（李大猫）</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>07-21山东</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>6a824f6e0000000033013513</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>6a824f6e0000000033013513_c001</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>姐妹们，我找到啦，在附近的幼儿园托管</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>郑郑好好</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>08-24山东</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>6a824f6e0000000033013513</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>6a824f6e0000000033013513_c002</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>我问了博雅的幼儿园 说是满员了 您是选的那个吗</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>家长BT</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>08-26山东</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>6a824f6e0000000033013513</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>6a824f6e0000000033013513_c003</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>有早托么</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>家长BU</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>08-28山东</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>6a824f6e0000000033013513</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>6a824f6e0000000033013513_c004</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>绿沅幼儿园</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>家长BV</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>08-29山东</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>6a824f6e0000000033013513</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>6a824f6e0000000033013513_c005</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>我们吃的那家挺好，22号楼，老师很负责</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>家长BW</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>08-24山东</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>6a824f6e0000000033013513</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>6a824f6e0000000033013513_c006</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>请问您选的哪个晚托啊</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>家长BT</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>08-26山东</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>6a824f6e0000000033013513</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>6a824f6e0000000033013513_c007</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>蹲蹲</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>家长BX</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>08-24山东</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>6a824f6e0000000033013513</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>6a824f6e0000000033013513_c008</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>同问 找到了吗</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>家长BT</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>08-23山东</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>xiaohongshu</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>6a824f6e0000000033013513</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>6a824f6e0000000033013513_c009</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>泉景老多小饭桌了</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>家长BY</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>08-31山东</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>03_xiaohongshu/comments.csv</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
+  <autoFilter ref="A1:N113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
